--- a/docs/task-distribution.xlsx
+++ b/docs/task-distribution.xlsx
@@ -1314,7 +1314,11 @@
           <t>exception/EntityNotFoundException.java</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n"/>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>exception/consultation/ConsultationHasCaseException.java</t>
+        </is>
+      </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
           <t>exception/case_/IncompleteSchedulingTaskException.java</t>
@@ -1338,11 +1342,7 @@
           <t>exception/document/MissingRequiredDocumentException.java</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>state/consultation/ConsultationState.java</t>
-        </is>
-      </c>
+      <c r="B21" s="29" t="n"/>
       <c r="C21" s="16" t="inlineStr">
         <is>
           <t>exception/case_/IncompleteBillingTaskException.java</t>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/PendingConsultationState.java</t>
+          <t>state/consultation/ConsultationState.java</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/AcceptedByPartnerConsultationState.java</t>
+          <t>state/consultation/PendingConsultationState.java</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/RejectedByPartnerConsultationState.java</t>
+          <t>state/consultation/AcceptedByPartnerConsultationState.java</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -1452,10 +1452,14 @@
       <c r="A25" s="29" t="n"/>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/ScheduledConsultationState.java</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="n"/>
+          <t>state/consultation/RejectedByPartnerConsultationState.java</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>exception/case_/UnsettledBillingException.java</t>
+        </is>
+      </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
           <t>state/finance/UnpaidInvoiceState.java</t>
@@ -1480,14 +1484,10 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/AcceptedByAssociateConsultationState.java</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>state/case_/CaseState.java</t>
-        </is>
-      </c>
+          <t>state/consultation/ScheduledConsultationState.java</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n"/>
       <c r="D26" s="17" t="inlineStr">
         <is>
           <t>state/finance/PaidInvoiceState.java</t>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>state/consultation/RejectedByAssociateConsultationState.java</t>
+          <t>state/consultation/AcceptedByAssociateConsultationState.java</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>state/case_/OpenCaseState.java</t>
+          <t>state/case_/CaseState.java</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -1538,10 +1538,14 @@
           <t>strategy/DenyAccessStrategy.java</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n"/>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>state/consultation/RejectedByAssociateConsultationState.java</t>
+        </is>
+      </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>state/case_/ClosedCaseState.java</t>
+          <t>state/case_/OpenCaseState.java</t>
         </is>
       </c>
       <c r="D28" s="29" t="n"/>
@@ -1567,7 +1571,11 @@
           <t>service/ConsultationService.java</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n"/>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>state/case_/ClosedCaseState.java</t>
+        </is>
+      </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
           <t>service/TransactionService.java</t>
@@ -1701,11 +1709,7 @@
         </is>
       </c>
       <c r="D34" s="29" t="n"/>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>exception/user/UnpaidInvoiceException.java</t>
-        </is>
-      </c>
+      <c r="E34" s="18" t="n"/>
       <c r="F34" s="19" t="inlineStr">
         <is>
           <t>partner/event-list.html</t>
@@ -2677,7 +2681,7 @@
         </is>
       </c>
       <c r="C3" s="24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="24" t="n">
         <v>24</v>
@@ -2695,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="24" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -2710,7 +2714,7 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="25" t="n">
         <v>9</v>
@@ -2728,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -2776,7 +2780,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="23" t="n">
         <v>27</v>
@@ -2794,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="B8" s="28" t="n"/>
       <c r="C8" s="28" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" s="28" t="n">
         <v>81</v>
@@ -2856,7 +2860,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -2867,7 +2871,7 @@
       </c>
       <c r="B9" s="28" t="n"/>
       <c r="C9" s="28" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="D9" s="28" t="n">
         <v>13.5</v>
@@ -2885,7 +2889,7 @@
         <v>1.5</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/task-distribution.xlsx
+++ b/docs/task-distribution.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>dto/consultation/SubmitOnlineConsultationRequest.java</t>
+          <t>dto/consultation/RequestOnlineConsultationRequest.java</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>dto/consultation/SubmitWalkInConsultationRequest.java</t>
+          <t>dto/consultation/RequestWalkInConsultationRequest.java</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
